--- a/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Class_by_Sample_Layer.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Class_by_Sample_Layer.xlsx
@@ -632,10 +632,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>28.4481873777126</v>
+        <v>28.4546076167823</v>
       </c>
       <c r="D2" t="n">
-        <v>0.906443970678112</v>
+        <v>0.906870450926227</v>
       </c>
     </row>
     <row r="3">
@@ -646,10 +646,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>17.514646887599</v>
+        <v>17.5108011150236</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75366513336602</v>
+        <v>1.75333473569397</v>
       </c>
     </row>
     <row r="4">
@@ -660,10 +660,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>17.4383623802787</v>
+        <v>17.4335608237773</v>
       </c>
       <c r="D4" t="n">
-        <v>0.57404082297464</v>
+        <v>0.573903827456795</v>
       </c>
     </row>
     <row r="5">
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>9.33859538197771</v>
+        <v>9.34193401787575</v>
       </c>
       <c r="D5" t="n">
-        <v>0.606558385367057</v>
+        <v>0.606789967741097</v>
       </c>
     </row>
     <row r="6">
@@ -688,10 +688,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>8.89070541448611</v>
+        <v>8.89210505783201</v>
       </c>
       <c r="D6" t="n">
-        <v>1.69812350606266</v>
+        <v>1.69844039351303</v>
       </c>
     </row>
     <row r="7">
@@ -702,7 +702,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>6.0952094129783</v>
+        <v>6.09481794786706</v>
       </c>
       <c r="D7"/>
     </row>
@@ -714,10 +714,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>3.22608947813918</v>
+        <v>3.22543327786321</v>
       </c>
       <c r="D8" t="n">
-        <v>0.652462783436685</v>
+        <v>0.65231206138855</v>
       </c>
     </row>
     <row r="9">
@@ -728,10 +728,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>2.61567542300022</v>
+        <v>2.61572166037823</v>
       </c>
       <c r="D9" t="n">
-        <v>0.266309172716062</v>
+        <v>0.266328161330401</v>
       </c>
     </row>
     <row r="10">
@@ -742,10 +742,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>2.12221346618614</v>
+        <v>2.12151181288669</v>
       </c>
       <c r="D10" t="n">
-        <v>0.588657670421057</v>
+        <v>0.588465550326627</v>
       </c>
     </row>
     <row r="11">
@@ -756,10 +756,10 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>1.27604330034489</v>
+        <v>1.27570358577485</v>
       </c>
       <c r="D11" t="n">
-        <v>0.286174586870707</v>
+        <v>0.286113399427014</v>
       </c>
     </row>
     <row r="12">
@@ -770,10 +770,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>1.13570354228655</v>
+        <v>1.13533792434292</v>
       </c>
       <c r="D12" t="n">
-        <v>0.295003082334226</v>
+        <v>0.294899459749859</v>
       </c>
     </row>
     <row r="13">
@@ -784,10 +784,10 @@
         <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>0.842819608971247</v>
+        <v>0.843016143430554</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0557464320292799</v>
+        <v>0.0557795981523561</v>
       </c>
     </row>
     <row r="14">
@@ -798,10 +798,10 @@
         <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>0.564474994923797</v>
+        <v>0.564279560192745</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0340832466395912</v>
+        <v>0.0340714462052048</v>
       </c>
     </row>
     <row r="15">
@@ -812,10 +812,10 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>0.198168603278418</v>
+        <v>0.198099992572837</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0102348477225202</v>
+        <v>0.0102313041736828</v>
       </c>
     </row>
     <row r="16">
@@ -826,10 +826,10 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>0.144123624177585</v>
+        <v>0.144073725135143</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0849243589434293</v>
+        <v>0.0848949561011439</v>
       </c>
     </row>
     <row r="17">
@@ -840,10 +840,10 @@
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0889305135628142</v>
+        <v>0.0889659391173463</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0193712470556227</v>
+        <v>0.0193723438294962</v>
       </c>
     </row>
     <row r="18">
@@ -854,7 +854,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="D18"/>
     </row>
@@ -866,7 +866,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0300252950484096</v>
+        <v>0.0300148995738265</v>
       </c>
       <c r="D19"/>
     </row>
@@ -903,10 +903,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>23.3612137867635</v>
+        <v>23.3603020190335</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1971715179072</v>
+        <v>1.1970265456348</v>
       </c>
     </row>
     <row r="3">
@@ -917,10 +917,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>18.7585675464447</v>
+        <v>18.7596754229218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.445227623743765</v>
+        <v>0.445256521377909</v>
       </c>
     </row>
     <row r="4">
@@ -931,10 +931,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>15.4088131875933</v>
+        <v>15.4088719795948</v>
       </c>
       <c r="D4" t="n">
-        <v>10.7345361992899</v>
+        <v>10.7344944659556</v>
       </c>
     </row>
     <row r="5">
@@ -945,10 +945,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>9.40355910464993</v>
+        <v>9.40208923435333</v>
       </c>
       <c r="D5" t="n">
-        <v>1.18539970027753</v>
+        <v>1.18527611735938</v>
       </c>
     </row>
     <row r="6">
@@ -959,10 +959,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.52226773244864</v>
+        <v>8.52260406917164</v>
       </c>
       <c r="D6" t="n">
-        <v>0.083296421579139</v>
+        <v>0.0833062168470663</v>
       </c>
     </row>
     <row r="7">
@@ -973,10 +973,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>5.75200313986558</v>
+        <v>5.75290790518388</v>
       </c>
       <c r="D7" t="n">
-        <v>1.01899653575214</v>
+        <v>1.01917258605361</v>
       </c>
     </row>
     <row r="8">
@@ -987,10 +987,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>5.50235662250732</v>
+        <v>5.50252043016617</v>
       </c>
       <c r="D8" t="n">
-        <v>0.800444125543568</v>
+        <v>0.80046181295353</v>
       </c>
     </row>
     <row r="9">
@@ -1001,10 +1001,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>4.34393527695431</v>
+        <v>4.34320640356764</v>
       </c>
       <c r="D9" t="n">
-        <v>1.10234302665655</v>
+        <v>1.10215673471252</v>
       </c>
     </row>
     <row r="10">
@@ -1015,10 +1015,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>2.72315175441127</v>
+        <v>2.72301279020991</v>
       </c>
       <c r="D10" t="n">
-        <v>0.119683381183223</v>
+        <v>0.119670820428728</v>
       </c>
     </row>
     <row r="11">
@@ -1029,10 +1029,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>1.73603927064758</v>
+        <v>1.73634246894241</v>
       </c>
       <c r="D11" t="n">
-        <v>0.137986526107818</v>
+        <v>0.138006835212184</v>
       </c>
     </row>
     <row r="12">
@@ -1043,10 +1043,10 @@
         <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>1.58574655495638</v>
+        <v>1.5857200763407</v>
       </c>
       <c r="D12" t="n">
-        <v>0.149916665967348</v>
+        <v>0.149933979851808</v>
       </c>
     </row>
     <row r="13">
@@ -1057,10 +1057,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>1.14559929153654</v>
+        <v>1.14591544718196</v>
       </c>
       <c r="D13" t="n">
-        <v>0.096593645700778</v>
+        <v>0.0966134880695889</v>
       </c>
     </row>
     <row r="14">
@@ -1071,10 +1071,10 @@
         <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>0.533191579369875</v>
+        <v>0.533244440897158</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0473778828666499</v>
+        <v>0.0473843566599068</v>
       </c>
     </row>
     <row r="15">
@@ -1085,10 +1085,10 @@
         <v>34</v>
       </c>
       <c r="C15" t="n">
-        <v>0.335446007240345</v>
+        <v>0.335502608919009</v>
       </c>
       <c r="D15" t="n">
-        <v>0.145391150819068</v>
+        <v>0.145399331381891</v>
       </c>
     </row>
     <row r="16">
@@ -1099,10 +1099,10 @@
         <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>0.313011764481159</v>
+        <v>0.313003479629514</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0264669082796906</v>
+        <v>0.0264561600207882</v>
       </c>
     </row>
     <row r="17">
@@ -1113,10 +1113,10 @@
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.253850907049785</v>
+        <v>0.253812213615222</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07776340641984</v>
+        <v>0.0777507059732587</v>
       </c>
     </row>
     <row r="18">
@@ -1127,10 +1127,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>0.164086084687455</v>
+        <v>0.164103314192489</v>
       </c>
       <c r="D18" t="n">
-        <v>0.100158054529747</v>
+        <v>0.100180123502046</v>
       </c>
     </row>
     <row r="19">
@@ -1141,10 +1141,10 @@
         <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0980842454091233</v>
+        <v>0.0980799672171447</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0230756382404663</v>
+        <v>0.0230733844377137</v>
       </c>
     </row>
     <row r="20">
@@ -1155,7 +1155,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0437381858883574</v>
+        <v>0.0437387712383516</v>
       </c>
       <c r="D20"/>
     </row>
@@ -1167,7 +1167,7 @@
         <v>35</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00657407331009671</v>
+        <v>0.00657693619591377</v>
       </c>
       <c r="D21"/>
     </row>
@@ -1179,7 +1179,7 @@
         <v>27</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="D22"/>
     </row>
@@ -1191,7 +1191,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00438194189213154</v>
+        <v>0.00438501071358667</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1541,10 +1541,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>24.6421608383319</v>
+        <v>24.6417854302772</v>
       </c>
       <c r="D2" t="n">
-        <v>4.50858756758852</v>
+        <v>4.50850291956916</v>
       </c>
     </row>
     <row r="3">
@@ -1555,10 +1555,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>21.9561628285138</v>
+        <v>21.9557849726509</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16771398525829</v>
+        <v>1.16769782773181</v>
       </c>
     </row>
     <row r="4">
@@ -1569,10 +1569,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2655397706116</v>
+        <v>19.2658310749008</v>
       </c>
       <c r="D4" t="n">
-        <v>0.801037083083817</v>
+        <v>0.801053720061133</v>
       </c>
     </row>
     <row r="5">
@@ -1583,10 +1583,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>6.2228881538803</v>
+        <v>6.22275973219218</v>
       </c>
       <c r="D5" t="n">
-        <v>0.90493038320812</v>
+        <v>0.904867016254575</v>
       </c>
     </row>
     <row r="6">
@@ -1597,10 +1597,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>6.10508864450461</v>
+        <v>6.10521387931923</v>
       </c>
       <c r="D6" t="n">
-        <v>0.159677371994831</v>
+        <v>0.159678792391499</v>
       </c>
     </row>
     <row r="7">
@@ -1611,10 +1611,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>6.10344626803667</v>
+        <v>6.10348415397392</v>
       </c>
       <c r="D7" t="n">
-        <v>0.999226949840471</v>
+        <v>0.999252870800103</v>
       </c>
     </row>
     <row r="8">
@@ -1625,10 +1625,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>3.93840198783546</v>
+        <v>3.93853124820496</v>
       </c>
       <c r="D8" t="n">
-        <v>2.37820589277897</v>
+        <v>2.37830413975467</v>
       </c>
     </row>
     <row r="9">
@@ -1639,10 +1639,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>3.75698155890424</v>
+        <v>3.75746277574264</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0471719743357626</v>
+        <v>0.0471755139183538</v>
       </c>
     </row>
     <row r="10">
@@ -1653,10 +1653,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>2.68983581567514</v>
+        <v>2.68972901058529</v>
       </c>
       <c r="D10" t="n">
-        <v>0.324633621661211</v>
+        <v>0.324586081290426</v>
       </c>
     </row>
     <row r="11">
@@ -1667,10 +1667,10 @@
         <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>1.14667551612367</v>
+        <v>1.1465334653637</v>
       </c>
       <c r="D11" t="n">
-        <v>0.369766800613695</v>
+        <v>0.36969012059224</v>
       </c>
     </row>
     <row r="12">
@@ -1681,10 +1681,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>0.956395560811265</v>
+        <v>0.956500761814801</v>
       </c>
       <c r="D12" t="n">
-        <v>0.101961225414945</v>
+        <v>0.101967492441141</v>
       </c>
     </row>
     <row r="13">
@@ -1695,10 +1695,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>0.867045093700098</v>
+        <v>0.867042172327682</v>
       </c>
       <c r="D13" t="n">
-        <v>0.40737851693052</v>
+        <v>0.40737673228615</v>
       </c>
     </row>
     <row r="14">
@@ -1709,10 +1709,10 @@
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>0.85322716181884</v>
+        <v>0.853300423066121</v>
       </c>
       <c r="D14" t="n">
-        <v>0.041449296587042</v>
+        <v>0.041446295080044</v>
       </c>
     </row>
     <row r="15">
@@ -1723,10 +1723,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.583402176979545</v>
+        <v>0.583290982760341</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0870314764808729</v>
+        <v>0.0870157783826704</v>
       </c>
     </row>
     <row r="16">
@@ -1737,10 +1737,10 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>0.407956245260099</v>
+        <v>0.407987245009878</v>
       </c>
       <c r="D16" t="n">
-        <v>0.04072813612845</v>
+        <v>0.0407363638337707</v>
       </c>
     </row>
     <row r="17">
@@ -1751,10 +1751,10 @@
         <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>0.248186503237012</v>
+        <v>0.248133636643862</v>
       </c>
       <c r="D17" t="n">
-        <v>0.107093733977408</v>
+        <v>0.107074311279528</v>
       </c>
     </row>
     <row r="18">
@@ -1765,7 +1765,7 @@
         <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0794954454718848</v>
+        <v>0.0794804603356408</v>
       </c>
       <c r="D18"/>
     </row>
@@ -1777,10 +1777,10 @@
         <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>0.063016756916131</v>
+        <v>0.0630217691918993</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0106182411349641</v>
+        <v>0.0106206001393996</v>
       </c>
     </row>
     <row r="20">
@@ -1791,10 +1791,10 @@
         <v>24</v>
       </c>
       <c r="C20" t="n">
-        <v>0.051623866740213</v>
+        <v>0.0516379046782591</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0104755880492871</v>
+        <v>0.0104789957127142</v>
       </c>
     </row>
     <row r="21">
@@ -1805,7 +1805,7 @@
         <v>35</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0286275448625279</v>
+        <v>0.0286216562756727</v>
       </c>
       <c r="D21"/>
     </row>
@@ -1817,7 +1817,7 @@
         <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0215354993342044</v>
+        <v>0.0215518136787733</v>
       </c>
       <c r="D22"/>
     </row>
@@ -1829,7 +1829,7 @@
         <v>42</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00769163117802357</v>
+        <v>0.00769723967014162</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1841,7 +1841,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00461513127313722</v>
+        <v>0.00461819133621055</v>
       </c>
       <c r="D24"/>
     </row>
@@ -1878,10 +1878,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>41.1226965728078</v>
+        <v>41.1181544407592</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1629152439783</v>
+        <v>1.16271391267712</v>
       </c>
     </row>
     <row r="3">
@@ -1892,10 +1892,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7689096094384</v>
+        <v>17.7671681883633</v>
       </c>
       <c r="D3" t="n">
-        <v>4.29432767302716</v>
+        <v>4.2937372628676</v>
       </c>
     </row>
     <row r="4">
@@ -1906,10 +1906,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>12.5118933543116</v>
+        <v>12.5158221148857</v>
       </c>
       <c r="D4" t="n">
-        <v>4.84513813620268</v>
+        <v>4.84664378215444</v>
       </c>
     </row>
     <row r="5">
@@ -1920,10 +1920,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>10.6290535606668</v>
+        <v>10.6283808772554</v>
       </c>
       <c r="D5" t="n">
-        <v>5.72148293638644</v>
+        <v>5.72085521364488</v>
       </c>
     </row>
     <row r="6">
@@ -1934,7 +1934,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>5.12700882116796</v>
+        <v>5.12663012137111</v>
       </c>
       <c r="D6"/>
     </row>
@@ -1946,10 +1946,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5410657193669</v>
+        <v>4.54254025821407</v>
       </c>
       <c r="D7" t="n">
-        <v>1.26372211027965</v>
+        <v>1.26424553476954</v>
       </c>
     </row>
     <row r="8">
@@ -1960,10 +1960,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>3.42924529730402</v>
+        <v>3.4306325226418</v>
       </c>
       <c r="D8" t="n">
-        <v>1.30875082780457</v>
+        <v>1.30926703969254</v>
       </c>
     </row>
     <row r="9">
@@ -1974,10 +1974,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1.21751116830729</v>
+        <v>1.2177090508129</v>
       </c>
       <c r="D9" t="n">
-        <v>0.489497778370004</v>
+        <v>0.489615016945174</v>
       </c>
     </row>
     <row r="10">
@@ -1988,10 +1988,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>1.09845515103157</v>
+        <v>1.09861161623602</v>
       </c>
       <c r="D10" t="n">
-        <v>0.259735777881981</v>
+        <v>0.259767490523437</v>
       </c>
     </row>
     <row r="11">
@@ -2002,10 +2002,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0764610187463</v>
+        <v>1.07669850745551</v>
       </c>
       <c r="D11" t="n">
-        <v>0.186974950143159</v>
+        <v>0.18702418051521</v>
       </c>
     </row>
     <row r="12">
@@ -2016,10 +2016,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>1.00397858421297</v>
+        <v>1.003900417609</v>
       </c>
       <c r="D12" t="n">
-        <v>0.163119185613959</v>
+        <v>0.163084629387419</v>
       </c>
     </row>
     <row r="13">
@@ -2030,10 +2030,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>0.272068552038335</v>
+        <v>0.272095187481516</v>
       </c>
       <c r="D13" t="n">
-        <v>0.112442581800846</v>
+        <v>0.112472967401727</v>
       </c>
     </row>
     <row r="14">
@@ -2044,7 +2044,7 @@
         <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>0.106510209713172</v>
+        <v>0.106529229357992</v>
       </c>
       <c r="D14"/>
     </row>
@@ -2056,7 +2056,7 @@
         <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0745489076284746</v>
+        <v>0.0745232685650044</v>
       </c>
       <c r="D15"/>
     </row>
@@ -2068,7 +2068,7 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0205934732585021</v>
+        <v>0.0206041989915073</v>
       </c>
       <c r="D16"/>
     </row>
@@ -2105,10 +2105,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>56.2950113123006</v>
+        <v>56.3041081219849</v>
       </c>
       <c r="D2" t="n">
-        <v>13.8490255669441</v>
+        <v>13.856182263946</v>
       </c>
     </row>
     <row r="3">
@@ -2119,10 +2119,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>17.0508572343531</v>
+        <v>17.0352886501756</v>
       </c>
       <c r="D3" t="n">
-        <v>4.68457221441722</v>
+        <v>4.67777158284229</v>
       </c>
     </row>
     <row r="4">
@@ -2133,10 +2133,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>9.00862099460801</v>
+        <v>9.00828755411928</v>
       </c>
       <c r="D4" t="n">
-        <v>2.02215732061012</v>
+        <v>2.02190812977588</v>
       </c>
     </row>
     <row r="5">
@@ -2147,10 +2147,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>5.88310231003368</v>
+        <v>5.88431086826985</v>
       </c>
       <c r="D5" t="n">
-        <v>0.138331607450938</v>
+        <v>0.138386538948105</v>
       </c>
     </row>
     <row r="6">
@@ -2161,10 +2161,10 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>4.65985259507985</v>
+        <v>4.66228845333324</v>
       </c>
       <c r="D6" t="n">
-        <v>3.20270178727532</v>
+        <v>3.20458350215252</v>
       </c>
     </row>
     <row r="7">
@@ -2175,10 +2175,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>2.07571960745581</v>
+        <v>2.07617088760931</v>
       </c>
       <c r="D7" t="n">
-        <v>0.495033498552083</v>
+        <v>0.495069019223064</v>
       </c>
     </row>
     <row r="8">
@@ -2189,10 +2189,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1.98068645471414</v>
+        <v>1.98260103785225</v>
       </c>
       <c r="D8" t="n">
-        <v>0.40990712214849</v>
+        <v>0.410246235998562</v>
       </c>
     </row>
     <row r="9">
@@ -2203,10 +2203,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.967041921835672</v>
+        <v>0.967424695406141</v>
       </c>
       <c r="D9" t="n">
-        <v>0.137633057761389</v>
+        <v>0.137743280417042</v>
       </c>
     </row>
     <row r="10">
@@ -2217,10 +2217,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>0.653944782403579</v>
+        <v>0.653790508001574</v>
       </c>
       <c r="D10" t="n">
-        <v>0.133944302900671</v>
+        <v>0.133970579529824</v>
       </c>
     </row>
     <row r="11">
@@ -2231,10 +2231,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.42055134000046</v>
+        <v>0.420978721028352</v>
       </c>
       <c r="D11" t="n">
-        <v>0.251217866740883</v>
+        <v>0.251600768850808</v>
       </c>
     </row>
     <row r="12">
@@ -2245,10 +2245,10 @@
         <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>0.294797111390009</v>
+        <v>0.294801554152728</v>
       </c>
       <c r="D12" t="n">
-        <v>0.060127286461208</v>
+        <v>0.0601038972054638</v>
       </c>
     </row>
     <row r="13">
@@ -2259,7 +2259,7 @@
         <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>0.273245290917606</v>
+        <v>0.273220773321349</v>
       </c>
       <c r="D13"/>
     </row>
@@ -2271,10 +2271,10 @@
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>0.168256946602726</v>
+        <v>0.168249505706103</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0369109208262652</v>
+        <v>0.0368418965963167</v>
       </c>
     </row>
     <row r="15">
@@ -2285,10 +2285,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.110220518298119</v>
+        <v>0.110260935136766</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0450243073135336</v>
+        <v>0.0450239683206631</v>
       </c>
     </row>
     <row r="16">
@@ -2299,10 +2299,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0905129096455505</v>
+        <v>0.0906268818335357</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0213347951269941</v>
+        <v>0.0213609609007617</v>
       </c>
     </row>
     <row r="17">
@@ -2313,7 +2313,7 @@
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0374081938479166</v>
+        <v>0.0373818914578821</v>
       </c>
       <c r="D17"/>
     </row>
@@ -2325,10 +2325,10 @@
         <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>0.030170476513252</v>
+        <v>0.0302089606111786</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00304767836202143</v>
+        <v>0.00305156584296595</v>
       </c>
     </row>
   </sheetData>
@@ -2364,10 +2364,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>39.7281014519403</v>
+        <v>39.7290616830707</v>
       </c>
       <c r="D2" t="n">
-        <v>6.21860820764229</v>
+        <v>6.21835232915755</v>
       </c>
     </row>
     <row r="3">
@@ -2378,10 +2378,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>34.8879985888077</v>
+        <v>34.8859603682263</v>
       </c>
       <c r="D3" t="n">
-        <v>4.42073812416722</v>
+        <v>4.42043960561398</v>
       </c>
     </row>
     <row r="4">
@@ -2392,10 +2392,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>7.53251208659025</v>
+        <v>7.53238581525108</v>
       </c>
       <c r="D4" t="n">
-        <v>0.237454364070223</v>
+        <v>0.237447338734724</v>
       </c>
     </row>
     <row r="5">
@@ -2406,10 +2406,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>5.97272540778288</v>
+        <v>5.9731093547609</v>
       </c>
       <c r="D5" t="n">
-        <v>0.503966138620791</v>
+        <v>0.504017630838705</v>
       </c>
     </row>
     <row r="6">
@@ -2420,10 +2420,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>4.48905867478099</v>
+        <v>4.48954446473964</v>
       </c>
       <c r="D6" t="n">
-        <v>0.579221982968712</v>
+        <v>0.579250875121448</v>
       </c>
     </row>
     <row r="7">
@@ -2434,10 +2434,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>3.25694228270683</v>
+        <v>3.25710668864576</v>
       </c>
       <c r="D7" t="n">
-        <v>0.70733559831466</v>
+        <v>0.707350658262006</v>
       </c>
     </row>
     <row r="8">
@@ -2448,10 +2448,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>1.14997350271633</v>
+        <v>1.15002814576828</v>
       </c>
       <c r="D8" t="n">
-        <v>0.640721303037778</v>
+        <v>0.640757070135462</v>
       </c>
     </row>
     <row r="9">
@@ -2462,10 +2462,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>0.940671348608249</v>
+        <v>0.94058433329486</v>
       </c>
       <c r="D9" t="n">
-        <v>0.633698989123858</v>
+        <v>0.633623359437904</v>
       </c>
     </row>
     <row r="10">
@@ -2476,10 +2476,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>0.558108885552207</v>
+        <v>0.558162676090998</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0461198226177086</v>
+        <v>0.0461237017220785</v>
       </c>
     </row>
     <row r="11">
@@ -2490,10 +2490,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>0.494833544322251</v>
+        <v>0.494917936870067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0431730031535043</v>
+        <v>0.043185765399925</v>
       </c>
     </row>
     <row r="12">
@@ -2504,10 +2504,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>0.35006731271956</v>
+        <v>0.350143473310065</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0186100260221621</v>
+        <v>0.0186156707426802</v>
       </c>
     </row>
     <row r="13">
@@ -2518,10 +2518,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2535018465008</v>
+        <v>0.253525157028426</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0546702359334213</v>
+        <v>0.0546684509143556</v>
       </c>
     </row>
     <row r="14">
@@ -2532,10 +2532,10 @@
         <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>0.108401006922979</v>
+        <v>0.108387807070915</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0395979660187865</v>
+        <v>0.0395979486402563</v>
       </c>
     </row>
     <row r="15">
@@ -2546,7 +2546,7 @@
         <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0846707889820255</v>
+        <v>0.0846647635257898</v>
       </c>
       <c r="D15"/>
     </row>
@@ -2558,10 +2558,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0830568856388914</v>
+        <v>0.0830291559691872</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00740641882260892</v>
+        <v>0.00740165586562154</v>
       </c>
     </row>
     <row r="17">
@@ -2572,10 +2572,10 @@
         <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0500354950193752</v>
+        <v>0.0500356743516428</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0267642568796029</v>
+        <v>0.0267683469819272</v>
       </c>
     </row>
     <row r="18">
@@ -2586,10 +2586,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0437340857696056</v>
+        <v>0.0437491351519284</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0110594125551018</v>
+        <v>0.0110653480533512</v>
       </c>
     </row>
     <row r="19">
@@ -2600,7 +2600,7 @@
         <v>27</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0121851199534034</v>
+        <v>0.0121795150074924</v>
       </c>
       <c r="D19"/>
     </row>
@@ -2612,7 +2612,7 @@
         <v>28</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00342168468528117</v>
+        <v>0.00342385186597158</v>
       </c>
       <c r="D20"/>
     </row>
@@ -2790,10 +2790,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>91.3398672624444</v>
+        <v>91.3388555763495</v>
       </c>
       <c r="D2" t="n">
-        <v>0.861894170816569</v>
+        <v>0.862083393122336</v>
       </c>
     </row>
     <row r="3">
@@ -2804,10 +2804,10 @@
         <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>4.29739103414817</v>
+        <v>4.2998423207784</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0933524972452613</v>
+        <v>0.0933985187150417</v>
       </c>
     </row>
     <row r="4">
@@ -2818,10 +2818,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>2.65365987314772</v>
+        <v>2.65422690068221</v>
       </c>
       <c r="D4" t="n">
-        <v>0.213133545685691</v>
+        <v>0.213293722340893</v>
       </c>
     </row>
     <row r="5">
@@ -2832,10 +2832,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>0.747320717623923</v>
+        <v>0.746077164710204</v>
       </c>
       <c r="D5" t="n">
-        <v>0.406402116738848</v>
+        <v>0.405727238535615</v>
       </c>
     </row>
     <row r="6">
@@ -2846,10 +2846,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>0.298005242007987</v>
+        <v>0.297697170490835</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0245469511332483</v>
+        <v>0.0245026224151622</v>
       </c>
     </row>
     <row r="7">
@@ -2860,10 +2860,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.233212573726985</v>
+        <v>0.23305415970703</v>
       </c>
       <c r="D7" t="n">
-        <v>0.111575935118184</v>
+        <v>0.111513697356389</v>
       </c>
     </row>
     <row r="8">
@@ -2874,7 +2874,7 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>0.219769260139959</v>
+        <v>0.219623369698133</v>
       </c>
       <c r="D8"/>
     </row>
@@ -2886,7 +2886,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>0.081013606389594</v>
+        <v>0.0810849869124129</v>
       </c>
       <c r="D9"/>
     </row>
@@ -2898,10 +2898,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0625588957431237</v>
+        <v>0.0624143977927732</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00844884085840169</v>
+        <v>0.00842932580506875</v>
       </c>
     </row>
     <row r="11">
@@ -2912,10 +2912,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0447621133500903</v>
+        <v>0.044693130754824</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0189029136531948</v>
+        <v>0.0188349213869587</v>
       </c>
     </row>
     <row r="12">
@@ -2926,10 +2926,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0224394212781726</v>
+        <v>0.02243082212351</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000681580412900505</v>
+        <v>0.0000985696922639011</v>
       </c>
     </row>
   </sheetData>
@@ -2965,10 +2965,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>57.749669817486</v>
+        <v>57.7496769827619</v>
       </c>
       <c r="D2" t="n">
-        <v>32.8647341787643</v>
+        <v>32.8647330880515</v>
       </c>
     </row>
     <row r="3">
@@ -2979,7 +2979,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>31.1608311737856</v>
+        <v>31.1608281680983</v>
       </c>
       <c r="D3"/>
     </row>
@@ -2991,7 +2991,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>8.10635960191601</v>
+        <v>8.10635394396169</v>
       </c>
       <c r="D4"/>
     </row>
@@ -3003,7 +3003,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>2.98313940681246</v>
+        <v>2.98314090517806</v>
       </c>
       <c r="D5"/>
     </row>
@@ -3040,10 +3040,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>94.0187702741291</v>
+        <v>94.0396963929599</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8363407254187</v>
+        <v>29.8417603709548</v>
       </c>
     </row>
     <row r="3">
@@ -3054,10 +3054,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>2.46890703144531</v>
+        <v>2.46278487288434</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08710525321409</v>
+        <v>0.0870575126095609</v>
       </c>
     </row>
     <row r="4">
@@ -3068,10 +3068,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>0.760679645127287</v>
+        <v>0.759402820259848</v>
       </c>
       <c r="D4" t="n">
-        <v>0.116497598478017</v>
+        <v>0.116513645389048</v>
       </c>
     </row>
     <row r="5">
@@ -3082,10 +3082,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>0.668717486193244</v>
+        <v>0.66478054693638</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0195973921296859</v>
+        <v>0.0194820266702645</v>
       </c>
     </row>
     <row r="6">
@@ -3096,10 +3096,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>0.570724366816388</v>
+        <v>0.567713398141494</v>
       </c>
       <c r="D6" t="n">
-        <v>0.388472017279955</v>
+        <v>0.386431784779191</v>
       </c>
     </row>
     <row r="7">
@@ -3110,10 +3110,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.564676374514014</v>
+        <v>0.562772521004523</v>
       </c>
       <c r="D7" t="n">
-        <v>0.120104197176902</v>
+        <v>0.119891020436368</v>
       </c>
     </row>
     <row r="8">
@@ -3124,10 +3124,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>0.444117302840861</v>
+        <v>0.441503066619031</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0165552300912905</v>
+        <v>0.0164577879062501</v>
       </c>
     </row>
     <row r="9">
@@ -3138,10 +3138,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.190898338682771</v>
+        <v>0.190677332152804</v>
       </c>
       <c r="D9" t="n">
-        <v>0.064368226732903</v>
+        <v>0.0644377307378925</v>
       </c>
     </row>
     <row r="10">
@@ -3152,10 +3152,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.113316115693334</v>
+        <v>0.112649160697476</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00955278473866335</v>
+        <v>0.00949655946273129</v>
       </c>
     </row>
     <row r="11">
@@ -3166,10 +3166,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>0.105694253405797</v>
+        <v>0.105071841369835</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00655903092408336</v>
+        <v>0.00652037608813461</v>
       </c>
     </row>
     <row r="12">
@@ -3180,10 +3180,10 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0320131673348304</v>
+        <v>0.031824490762082</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00288790137493388</v>
+        <v>0.00287098879932759</v>
       </c>
     </row>
     <row r="13">
@@ -3194,10 +3194,10 @@
         <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02388287249898</v>
+        <v>0.023742169843383</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00467103303641761</v>
+        <v>0.00464364622282581</v>
       </c>
     </row>
     <row r="14">
@@ -3208,7 +3208,7 @@
         <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0116872199753333</v>
+        <v>0.0116185841261627</v>
       </c>
       <c r="D14"/>
     </row>
@@ -3220,7 +3220,7 @@
         <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00965475140130624</v>
+        <v>0.00959795172690207</v>
       </c>
       <c r="D15"/>
     </row>
@@ -3232,7 +3232,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="D16"/>
     </row>
@@ -3244,7 +3244,7 @@
         <v>35</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="D17"/>
     </row>
@@ -3256,7 +3256,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00203267884389815</v>
+        <v>0.00202063239926062</v>
       </c>
       <c r="D18"/>
     </row>
@@ -3293,10 +3293,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>29.8136808078009</v>
+        <v>29.8138062021027</v>
       </c>
       <c r="D2" t="n">
-        <v>1.55893687052557</v>
+        <v>1.55908885907971</v>
       </c>
     </row>
     <row r="3">
@@ -3307,10 +3307,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>18.1689234804074</v>
+        <v>18.1673264885753</v>
       </c>
       <c r="D3" t="n">
-        <v>0.432739320612276</v>
+        <v>0.432718841054423</v>
       </c>
     </row>
     <row r="4">
@@ -3321,10 +3321,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>11.2867641756239</v>
+        <v>11.2870459326145</v>
       </c>
       <c r="D4" t="n">
-        <v>7.79747841092047</v>
+        <v>7.79773733744146</v>
       </c>
     </row>
     <row r="5">
@@ -3335,10 +3335,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>9.01079721212342</v>
+        <v>9.01253857408425</v>
       </c>
       <c r="D5" t="n">
-        <v>0.103528975515545</v>
+        <v>0.103550337848236</v>
       </c>
     </row>
     <row r="6">
@@ -3349,10 +3349,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>8.94544697519405</v>
+        <v>8.94681254657371</v>
       </c>
       <c r="D6" t="n">
-        <v>1.43110346325025</v>
+        <v>1.43137024879891</v>
       </c>
     </row>
     <row r="7">
@@ -3363,10 +3363,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6.77989306604406</v>
+        <v>6.77881974051897</v>
       </c>
       <c r="D7" t="n">
-        <v>1.16354430973066</v>
+        <v>1.16335433995446</v>
       </c>
     </row>
     <row r="8">
@@ -3377,10 +3377,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>4.17942439810022</v>
+        <v>4.17865556908465</v>
       </c>
       <c r="D8" t="n">
-        <v>0.629474802709262</v>
+        <v>0.629336454614041</v>
       </c>
     </row>
     <row r="9">
@@ -3391,10 +3391,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>2.78975080444999</v>
+        <v>2.78941399814897</v>
       </c>
       <c r="D9" t="n">
-        <v>0.237114443555658</v>
+        <v>0.237065455423461</v>
       </c>
     </row>
     <row r="10">
@@ -3405,10 +3405,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>2.76752140081153</v>
+        <v>2.76760900747935</v>
       </c>
       <c r="D10" t="n">
-        <v>0.821765152469481</v>
+        <v>0.821789923031818</v>
       </c>
     </row>
     <row r="11">
@@ -3419,10 +3419,10 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>1.94620304946784</v>
+        <v>1.94666949763768</v>
       </c>
       <c r="D11" t="n">
-        <v>0.107228840321645</v>
+        <v>0.107272471208542</v>
       </c>
     </row>
     <row r="12">
@@ -3433,10 +3433,10 @@
         <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>1.54503415439421</v>
+        <v>1.54499986880777</v>
       </c>
       <c r="D12" t="n">
-        <v>0.250650727927502</v>
+        <v>0.250653674269885</v>
       </c>
     </row>
     <row r="13">
@@ -3447,10 +3447,10 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0631987894026</v>
+        <v>1.06308706922884</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0927383291354896</v>
+        <v>0.0927261331216983</v>
       </c>
     </row>
     <row r="14">
@@ -3461,10 +3461,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>0.524260671449889</v>
+        <v>0.524152306972405</v>
       </c>
       <c r="D14" t="n">
-        <v>0.323530587624025</v>
+        <v>0.323469312291106</v>
       </c>
     </row>
     <row r="15">
@@ -3475,10 +3475,10 @@
         <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>0.297590307020918</v>
+        <v>0.297553863194058</v>
       </c>
       <c r="D15" t="n">
-        <v>0.105589392066944</v>
+        <v>0.105597733144794</v>
       </c>
     </row>
     <row r="16">
@@ -3489,10 +3489,10 @@
         <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>0.26521902396207</v>
+        <v>0.26530472662009</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0206940780505517</v>
+        <v>0.0206946981035593</v>
       </c>
     </row>
     <row r="17">
@@ -3503,10 +3503,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.25487580782696</v>
+        <v>0.254814837259604</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0191447711243624</v>
+        <v>0.0191428227718087</v>
       </c>
     </row>
     <row r="18">
@@ -3517,10 +3517,10 @@
         <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>0.173577872758271</v>
+        <v>0.173568969952148</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0241654040245121</v>
+        <v>0.0241653376278085</v>
       </c>
     </row>
     <row r="19">
@@ -3531,7 +3531,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>0.11370582480294</v>
+        <v>0.113712742732618</v>
       </c>
       <c r="D19"/>
     </row>
@@ -3543,7 +3543,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0741321783585579</v>
+        <v>0.0741080584124175</v>
       </c>
       <c r="D20"/>
     </row>
